--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +820,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +840,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +883,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +944,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1079,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1204,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1971,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,7 +2015,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2002,35 +2026,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2087,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2106,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2142,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2203,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2222,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2258,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2319,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2338,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2363,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2439,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2483,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2494,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2507,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2517,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2555,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2610,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,7 +2638,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2671,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,35 +2726,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2787,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2903,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2958,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3019,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3038,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3074,3615 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -450,7 +450,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -835,14 +835,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -850,7 +850,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -893,24 +893,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1133,24 +1133,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1247,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1280,7 +1284,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1308,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1371,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1432,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1551,7 +1567,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1562,7 +1578,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1595,32 +1611,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1628,7 +1648,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1652,33 +1672,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1735,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1744,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,33 +1796,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1942,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2026,7 +2058,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2124,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2142,7 +2174,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2240,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2258,7 +2290,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2356,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2373,12 +2405,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2423,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2476,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2490,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,41 +2520,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2555,12 +2591,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2610,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2599,7 +2635,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2610,35 +2646,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2671,12 +2707,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2726,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2751,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2827,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2846,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2842,35 +2882,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2943,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2962,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +2987,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3019,12 +3063,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3082,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,46 +3107,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3183,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3202,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,7 +3227,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3190,35 +3238,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3251,12 +3299,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3318,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3295,46 +3343,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3367,12 +3419,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3438,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3411,18 +3463,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3491,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3445,7 +3501,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3455,40 +3511,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3562,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3512,33 +3572,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3551,60 +3615,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3628,33 +3696,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3739,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3677,7 +3749,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3687,40 +3759,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3734,7 +3810,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3744,17 +3820,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3764,13 +3840,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3863,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3793,7 +3873,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3803,40 +3883,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3934,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3860,17 +3944,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3880,13 +3964,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3987,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A56891D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3909,7 +3997,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3919,12 +4007,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3947,12 +4035,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3960,13 +4048,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4106,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4119,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4063,12 +4167,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4186,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4222,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4235,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4141,7 +4245,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4179,12 +4283,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4302,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,7 +4338,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4351,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4257,7 +4361,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4295,12 +4399,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4418,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,7 +4454,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4467,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4373,7 +4477,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4411,12 +4515,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4534,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,7 +4570,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4479,22 +4583,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4527,12 +4631,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4650,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,7 +4686,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4595,22 +4699,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4643,12 +4747,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4766,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4698,7 +4802,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4711,22 +4815,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4759,12 +4863,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4882,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,77 +4918,73 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4898,7 +4998,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4908,65 +5008,61 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4999,12 +5095,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5018,7 +5114,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5054,35 +5150,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5115,12 +5211,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5134,7 +5230,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5170,35 +5266,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5231,12 +5327,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5250,7 +5346,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5286,35 +5382,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5347,12 +5443,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5366,7 +5462,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5402,35 +5498,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5463,12 +5559,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5482,7 +5578,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5518,35 +5614,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5579,12 +5675,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5598,7 +5694,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5634,35 +5730,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5695,12 +5791,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5714,7 +5810,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5750,35 +5846,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5811,12 +5907,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5830,7 +5926,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5866,35 +5962,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5927,12 +6023,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5946,7 +6042,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5982,35 +6078,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6043,12 +6139,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6062,7 +6158,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6098,35 +6194,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6159,12 +6255,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6178,7 +6274,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6214,35 +6310,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6275,12 +6371,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6294,7 +6390,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6330,35 +6426,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6391,12 +6487,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6410,7 +6506,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6446,35 +6542,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6507,12 +6603,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6526,7 +6622,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6562,35 +6658,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6623,12 +6719,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6642,47 +6738,3243 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr">
+      <c r="AC72" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1892,7 +1896,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1916,17 +1920,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1936,13 +1940,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2047,7 +2055,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2124,7 +2132,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2240,7 +2248,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2356,7 +2364,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2476,7 +2484,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2596,7 +2604,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2712,7 +2720,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,7 +2840,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2948,7 +2956,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,7 +3076,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3188,7 +3196,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3304,7 +3312,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3358,7 +3366,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3432,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3478,77 +3486,73 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3562,7 +3566,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3572,37 +3576,33 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3615,24 +3615,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3645,12 +3645,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3863,24 +3863,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3893,24 +3893,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3987,32 +3987,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4048,29 +4048,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:46</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4095,7 +4079,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4119,7 +4103,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4129,7 +4113,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4139,12 +4123,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4167,12 +4151,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4180,13 +4164,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,60 +4235,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4302,7 +4306,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4312,17 +4316,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4332,13 +4336,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4351,22 +4359,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4399,12 +4407,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4418,7 +4426,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4467,22 +4475,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4515,12 +4523,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4583,7 +4591,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4593,7 +4601,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4631,12 +4639,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4650,7 +4658,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4699,22 +4707,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4752,7 +4760,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4815,22 +4823,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4863,12 +4871,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4882,7 +4890,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4931,22 +4939,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56891D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4979,12 +4987,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4998,7 +5006,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5047,22 +5055,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A56891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5100,7 +5108,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5163,7 +5171,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5173,7 +5181,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5211,12 +5219,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5230,7 +5238,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5279,22 +5287,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5327,12 +5335,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5346,7 +5354,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5395,22 +5403,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5443,12 +5451,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5511,22 +5519,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5559,12 +5567,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5578,7 +5586,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5627,22 +5635,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5675,12 +5683,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5743,22 +5751,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5796,7 +5804,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5810,7 +5818,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5859,22 +5867,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5907,12 +5915,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5975,7 +5983,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5985,7 +5993,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6023,12 +6031,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6042,7 +6050,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6091,22 +6099,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6139,12 +6147,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6207,22 +6215,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6255,12 +6263,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6274,7 +6282,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6323,22 +6331,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6371,12 +6379,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6390,7 +6398,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6439,22 +6447,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6492,7 +6500,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6506,7 +6514,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6555,22 +6563,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6608,7 +6616,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6622,7 +6630,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6671,22 +6679,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6719,12 +6727,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6738,7 +6746,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6787,22 +6795,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6835,12 +6843,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6854,7 +6862,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6879,22 +6887,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6907,22 +6911,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6960,7 +6964,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6974,7 +6978,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7009,82 +7013,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7108,17 +7108,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7133,40 +7133,40 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7199,12 +7199,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7297,24 +7297,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7391,59 +7391,55 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7462,7 +7458,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7472,17 +7468,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7492,17 +7488,13 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7515,24 +7507,24 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7545,34 +7537,34 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7586,7 +7578,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7621,12 +7613,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7639,60 +7631,64 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7706,7 +7702,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7716,33 +7712,37 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -7879,7 +7879,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7927,12 +7927,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7995,60 +7995,64 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8062,7 +8066,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8072,33 +8076,37 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8111,22 +8119,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8159,12 +8167,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8178,7 +8186,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8203,7 +8211,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8227,7 +8235,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8237,7 +8245,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8275,12 +8283,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8294,7 +8302,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8343,7 +8351,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8353,7 +8361,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8363,40 +8371,44 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8410,7 +8422,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8420,33 +8432,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8475,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8469,7 +8485,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8507,12 +8523,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8526,7 +8542,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8575,22 +8591,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8623,12 +8639,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8642,7 +8658,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8691,22 +8707,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8739,12 +8755,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8758,7 +8774,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8807,7 +8823,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8817,7 +8833,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8855,7 +8871,7 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8874,7 +8890,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8923,7 +8939,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8933,7 +8949,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8976,7 +8992,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8990,7 +9006,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9015,22 +9031,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9055,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9053,7 +9065,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9091,12 +9103,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9110,7 +9122,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9159,22 +9171,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9207,12 +9219,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9226,7 +9238,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9261,12 +9273,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9279,22 +9291,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9327,12 +9339,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9346,7 +9358,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9395,7 +9407,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9405,7 +9417,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9448,7 +9460,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9497,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9515,7 +9527,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9525,7 +9537,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9563,12 +9575,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9631,22 +9643,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9679,7 +9691,7 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9698,7 +9710,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9733,12 +9745,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9751,22 +9763,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9799,7 +9811,7 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9848,17 +9860,13 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9871,22 +9879,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9919,12 +9927,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9938,7 +9946,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9968,13 +9976,373 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD83"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,13 +720,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -840,17 +844,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -920,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1079,18 +1083,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1214,7 +1222,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1338,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1462,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1621,24 +1629,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1697,12 +1705,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1753,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1772,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1821,12 +1829,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1869,24 +1877,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1896,7 +1904,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1935,22 +1943,22 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1983,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2016,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2040,17 +2052,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2060,13 +2072,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2099,32 +2115,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2132,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2156,33 +2176,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2215,32 +2239,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2248,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2272,33 +2300,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2331,32 +2363,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2364,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,37 +2424,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2451,32 +2487,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2484,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2508,17 +2548,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2528,17 +2568,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2571,32 +2611,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2604,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2628,33 +2672,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2768,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2774,7 +2822,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,7 +3004,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3010,7 +3058,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3124,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3130,7 +3178,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3244,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3312,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3361,12 +3409,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3481,12 +3529,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3499,22 +3547,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3552,7 +3600,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3566,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3591,88 +3639,88 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3696,22 +3744,22 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3721,82 +3769,78 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3810,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3820,17 +3864,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3845,82 +3889,78 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3934,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3944,65 +3984,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4035,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4054,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4079,56 +4119,60 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4151,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4164,29 +4208,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>07:46</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>07:53</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4211,18 +4239,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4235,24 +4267,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4265,12 +4297,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -4287,12 +4319,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4306,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4331,22 +4363,22 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4359,52 +4391,56 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4412,7 +4448,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4426,7 +4462,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4436,33 +4472,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4515,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4485,7 +4525,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4495,40 +4535,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4542,7 +4586,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4552,33 +4596,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4639,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4601,7 +4649,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4639,12 +4687,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4658,7 +4706,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4683,7 +4731,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4707,32 +4755,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4755,12 +4803,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4768,13 +4816,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4799,7 +4863,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4823,7 +4887,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4833,7 +4897,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4843,40 +4907,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4890,7 +4958,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4900,33 +4968,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4939,7 +5011,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4949,7 +5021,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4959,40 +5031,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5006,7 +5082,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5016,33 +5092,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5135,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5065,7 +5145,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5075,40 +5155,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5122,7 +5206,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5132,33 +5216,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5259,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5181,7 +5269,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5219,12 +5307,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5238,7 +5326,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5287,7 +5375,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5297,7 +5385,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5335,12 +5423,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5354,7 +5442,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5403,7 +5491,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5413,7 +5501,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5423,40 +5511,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5470,7 +5562,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5480,33 +5572,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5615,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5529,7 +5625,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5539,12 +5635,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq47，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5567,12 +5663,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5580,13 +5676,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5635,7 +5747,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A56891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5645,7 +5757,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5683,12 +5795,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5702,7 +5814,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5751,7 +5863,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5761,7 +5873,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5799,12 +5911,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5818,7 +5930,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5867,32 +5979,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5915,12 +6027,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5928,13 +6040,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5983,22 +6111,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6031,12 +6159,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6050,7 +6178,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6099,7 +6227,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6109,7 +6237,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6147,12 +6275,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6166,7 +6294,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6215,7 +6343,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6225,7 +6353,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6268,7 +6396,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6282,7 +6410,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6331,7 +6459,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6341,7 +6469,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6379,12 +6507,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6398,7 +6526,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6447,7 +6575,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6457,7 +6585,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6495,12 +6623,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6514,7 +6642,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,7 +6691,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6573,7 +6701,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6611,12 +6739,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6630,7 +6758,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6679,22 +6807,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6732,7 +6860,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6746,7 +6874,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6795,22 +6923,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6843,12 +6971,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6862,7 +6990,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6911,22 +7039,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6959,12 +7087,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6978,7 +7106,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7003,22 +7131,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7031,22 +7155,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7084,7 +7208,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7098,7 +7222,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7123,22 +7247,18 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7151,22 +7271,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7204,7 +7324,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7218,7 +7338,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7243,7 +7363,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7261,70 +7381,66 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7338,7 +7454,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7348,65 +7464,61 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7439,12 +7551,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7458,7 +7570,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7483,7 +7595,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7494,77 +7606,73 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7578,7 +7686,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7588,17 +7696,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7613,82 +7721,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7702,7 +7806,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7712,17 +7816,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7737,82 +7841,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7826,7 +7926,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7836,17 +7936,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7861,40 +7961,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7927,12 +8027,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7946,7 +8046,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7971,7 +8071,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7982,77 +8082,73 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8066,7 +8162,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8076,17 +8172,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8096,45 +8192,41 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8167,12 +8259,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8186,7 +8278,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8211,46 +8303,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8283,12 +8379,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8302,7 +8398,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8327,88 +8423,88 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8422,7 +8518,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8432,17 +8528,17 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8457,40 +8553,40 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8523,12 +8619,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8542,7 +8638,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8567,18 +8663,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -8591,60 +8691,64 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8658,7 +8762,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8668,33 +8772,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8815,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8717,7 +8825,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8755,12 +8863,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8774,7 +8882,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8799,7 +8907,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8823,7 +8931,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8833,7 +8941,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8843,40 +8951,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8890,7 +9002,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8900,33 +9012,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8939,7 +9055,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8949,7 +9065,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8959,40 +9075,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9006,7 +9126,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9016,33 +9136,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9055,60 +9179,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9122,7 +9250,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9132,33 +9260,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9171,22 +9303,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9219,12 +9351,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9238,7 +9370,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9268,17 +9400,13 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9291,52 +9419,56 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9344,7 +9476,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9358,7 +9490,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9368,33 +9500,37 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9543,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9417,7 +9553,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9460,7 +9596,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9474,7 +9610,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9504,17 +9640,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9527,60 +9659,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9594,7 +9730,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9604,17 +9740,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9624,13 +9760,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9643,60 +9783,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9710,7 +9854,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9720,17 +9864,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9745,12 +9889,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9763,22 +9907,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9811,12 +9955,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9830,7 +9974,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9879,7 +10023,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9889,7 +10033,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9899,40 +10043,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9946,7 +10094,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9956,17 +10104,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9981,7 +10129,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -9999,7 +10147,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10009,7 +10157,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10019,40 +10167,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10066,7 +10218,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10076,17 +10228,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10101,12 +10253,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10119,22 +10271,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -10167,12 +10319,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10186,7 +10338,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10211,7 +10363,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10235,60 +10387,64 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10302,47 +10458,2407 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X83" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AD83" s="2" t="inlineStr">
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7404,17 +7404,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,17 +8148,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8520,17 +8520,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9512,17 +9512,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10256,17 +10256,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10628,17 +10628,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10992,17 +10992,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11364,17 +11364,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11779,32 +11779,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11812,7 +11816,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11836,17 +11840,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11856,17 +11860,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11899,32 +11903,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11932,7 +11940,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11956,17 +11964,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11976,17 +11984,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12019,32 +12027,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12052,7 +12064,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12076,17 +12088,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12096,17 +12108,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -12139,32 +12151,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12172,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12196,17 +12212,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12216,17 +12232,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12412,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12456,17 +12472,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12590,7 +12606,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12676,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12704,17 +12720,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12854,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13176,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13214,7 +13230,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13602,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13700,12 +13716,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
@@ -13780,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13834,7 +13850,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14164,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14208,17 +14224,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14300,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14420,7 +14436,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14474,7 +14490,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14556,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14584,12 +14600,12 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
@@ -14714,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14796,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14904,7 +14920,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15028,7 +15044,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15082,7 +15098,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15168,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15196,17 +15212,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15342,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15412,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15450,7 +15466,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -15636,7 +15652,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15680,17 +15696,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -15880,7 +15896,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15934,7 +15950,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16074,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16144,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16172,17 +16188,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16318,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16640,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16678,7 +16694,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16818,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17170,7 +17186,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17252,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17280,12 +17296,12 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
@@ -17484,7 +17500,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17528,17 +17544,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17624,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17662,7 +17678,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17748,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17776,12 +17792,12 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
@@ -17856,7 +17872,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18034,7 +18050,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18120,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18228,7 +18244,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18282,7 +18298,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18368,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18406,7 +18422,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18546,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18616,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18654,7 +18670,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18918,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19232,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19406,7 +19422,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19794,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19864,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -20026,7 +20042,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20112,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20140,12 +20156,12 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
@@ -20344,7 +20360,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20398,7 +20414,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20662,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -20770,7 +20786,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20910,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21220,7 +21236,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21264,12 +21280,12 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
@@ -21344,7 +21360,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21388,17 +21404,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21464,7 +21480,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21508,17 +21524,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21604,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21632,17 +21648,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21724,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21828,7 +21844,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21952,7 +21968,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22076,7 +22092,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22130,7 +22146,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22200,7 +22216,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22244,17 +22260,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -22324,7 +22340,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22378,7 +22394,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22448,7 +22464,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22502,7 +22518,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22626,7 +22642,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -22696,7 +22712,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22750,7 +22766,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22960,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22998,7 +23014,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23262,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23386,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23510,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23618,7 +23634,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23820,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23891,32 +23907,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23924,7 +23944,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23948,17 +23968,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23968,17 +23988,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24011,32 +24031,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -24044,7 +24068,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24068,17 +24092,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24088,12 +24112,12 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
@@ -24131,32 +24155,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24164,7 +24192,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24188,17 +24216,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24208,17 +24236,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24251,32 +24279,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -24284,7 +24316,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24308,17 +24340,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24328,12 +24360,12 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
@@ -24371,12 +24403,12 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -24404,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24412,10 +24444,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R194" s="2" t="inlineStr"/>
-      <c r="S194" s="2" t="inlineStr"/>
-      <c r="T194" s="2" t="inlineStr"/>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V194" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24458,7 +24506,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24491,32 +24539,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24524,7 +24576,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24548,17 +24600,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24568,17 +24620,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -24611,32 +24663,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24644,7 +24700,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24668,17 +24724,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24688,17 +24744,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24820,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24851,12 +24907,12 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -24884,7 +24940,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24892,10 +24948,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R198" s="2" t="inlineStr"/>
-      <c r="S198" s="2" t="inlineStr"/>
-      <c r="T198" s="2" t="inlineStr"/>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V198" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24938,7 +25010,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25076,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25058,7 +25130,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -25124,7 +25196,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25244,7 +25316,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25298,7 +25370,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25436,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25418,7 +25490,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25556,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25538,7 +25610,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -25604,7 +25676,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25728,7 +25800,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25772,17 +25844,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -25902,7 +25974,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26026,7 +26098,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26292,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26269,12 +26341,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26340,7 +26412,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26518,7 +26590,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26708,7 +26780,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26757,7 +26829,7 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -26832,7 +26904,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26876,17 +26948,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27006,7 +27078,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27202,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27374,7 +27446,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27570,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27688,7 +27760,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27732,17 +27804,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27812,7 +27884,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27856,17 +27928,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28056,7 +28128,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28105,12 +28177,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28230,7 +28302,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28422,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28474,7 +28546,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28598,7 +28670,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28664,7 +28736,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28908,7 +28980,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28952,17 +29024,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29032,7 +29104,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29081,7 +29153,7 @@
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
@@ -29210,7 +29282,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29458,7 +29530,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29528,7 +29600,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29572,17 +29644,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29778,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29968,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29957,12 +30029,12 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30086,7 +30158,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30210,7 +30282,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30276,7 +30348,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30332,17 +30404,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -30466,7 +30538,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30662,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30910,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -30962,7 +31034,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31282,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31458,7 +31530,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31582,7 +31654,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31902,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31954,7 +32026,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32150,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32394,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32570,7 +32642,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32694,7 +32766,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32764,7 +32836,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32808,17 +32880,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33066,7 +33138,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33190,7 +33262,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33382,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33452,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33504,7 +33576,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33553,7 +33625,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33682,7 +33754,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34000,7 +34072,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34049,12 +34121,12 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34120,7 +34192,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34164,17 +34236,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34298,7 +34370,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34440,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34412,17 +34484,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34666,7 +34738,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34790,7 +34862,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34860,7 +34932,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34904,17 +34976,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35038,7 +35110,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35286,7 +35358,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35410,7 +35482,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -35534,7 +35606,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35604,7 +35676,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35728,7 +35800,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35777,7 +35849,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -36100,7 +36172,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36149,12 +36221,12 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36224,7 +36296,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36268,17 +36340,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36402,7 +36474,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36718,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36716,7 +36788,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36760,17 +36832,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36966,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37014,7 +37086,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37084,7 +37156,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37128,17 +37200,17 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37262,7 +37334,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37382,7 +37454,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37648,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37673,24 +37745,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37700,7 +37772,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37749,12 +37821,12 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37797,24 +37869,24 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -37824,7 +37896,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37873,7 +37945,7 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -37911,32 +37983,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37944,7 +38020,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37968,17 +38044,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37988,17 +38064,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -38031,32 +38107,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -38064,7 +38144,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38088,17 +38168,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38108,17 +38188,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -38151,32 +38231,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38184,7 +38268,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38208,17 +38292,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38228,17 +38312,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38304,7 +38388,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38424,7 +38508,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38473,7 +38557,7 @@
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
@@ -38544,7 +38628,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38588,17 +38672,17 @@
       </c>
       <c r="AB309" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-operations.xlsx
+++ b/data/export/2026-09-28-operations.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5172,17 +5172,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6164,17 +6164,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10132,17 +10132,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10256,17 +10256,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11736,17 +11736,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12275,32 +12275,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12308,7 +12312,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12332,17 +12336,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12352,17 +12356,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12395,32 +12399,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12428,7 +12436,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12452,17 +12460,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12472,17 +12480,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12738,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12862,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13184,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13220,17 +13228,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13486,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13610,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13804,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13850,7 +13858,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14242,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14378,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14444,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14490,7 +14498,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14738,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14840,17 +14848,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14928,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15044,7 +15052,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15088,17 +15096,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15230,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15350,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15904,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16198,7 +16206,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16326,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16648,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16684,17 +16692,17 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16950,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17070,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17140,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17186,7 +17194,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17554,7 +17562,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17678,7 +17686,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17880,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17916,17 +17924,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18058,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -18120,7 +18128,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18244,7 +18252,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18288,17 +18296,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18554,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18624,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18918,7 +18926,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19174,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19422,7 +19430,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19802,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19926,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -20042,7 +20050,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20368,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20404,17 +20412,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20794,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21414,7 +21422,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21542,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21898,7 +21906,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21976,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22012,17 +22020,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -22270,7 +22278,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22348,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22464,7 +22472,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22508,17 +22516,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22642,7 +22650,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22720,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22766,7 +22774,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22890,7 +22898,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22968,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23014,7 +23022,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23386,7 +23394,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23642,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -23820,7 +23828,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23998,7 +24006,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -24630,7 +24638,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24762,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -24874,7 +24882,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -24912,7 +24920,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -24940,7 +24948,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25043,32 +25051,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -25076,7 +25088,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25100,17 +25112,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25120,17 +25132,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25163,32 +25175,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -25196,7 +25212,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25220,17 +25236,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25240,17 +25256,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -25283,32 +25299,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25316,7 +25336,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25340,17 +25360,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25360,17 +25380,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25456,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25490,7 +25510,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -25556,7 +25576,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25610,7 +25630,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25696,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25800,7 +25820,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25849,7 +25869,7 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -26222,7 +26242,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26412,7 +26432,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26456,17 +26476,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26800,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26824,17 +26844,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -27326,7 +27346,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -27690,7 +27710,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -27760,7 +27780,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27809,7 +27829,7 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
@@ -27884,7 +27904,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -28062,7 +28082,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -28736,7 +28756,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28780,17 +28800,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -29104,7 +29124,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29148,17 +29168,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29426,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29620,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29902,7 +29922,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31158,7 +31178,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -31406,7 +31426,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32290,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -32518,7 +32538,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32836,7 +32856,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32885,7 +32905,7 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
@@ -33452,7 +33472,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33496,17 +33516,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -33576,7 +33596,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33620,17 +33640,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33878,7 +33898,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -34002,7 +34022,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -34192,7 +34212,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34614,7 +34634,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -34932,7 +34952,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34981,7 +35001,7 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
@@ -35676,7 +35696,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35720,17 +35740,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -35800,7 +35820,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35844,17 +35864,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35978,7 +35998,7 @@
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -36102,7 +36122,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -36296,7 +36316,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36594,7 +36614,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37176,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37205,7 +37225,7 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
@@ -37578,7 +37598,7 @@
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -37648,7 +37668,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37692,17 +37712,17 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -37896,7 +37916,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37940,17 +37960,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -38144,7 +38164,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38241,24 +38261,24 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N306" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O306" s="2" t="inlineStr">
@@ -38268,7 +38288,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38317,7 +38337,7 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
@@ -38355,32 +38375,36 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -38388,7 +38412,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38412,17 +38436,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38432,17 +38456,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -38475,32 +38499,36 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr"/>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N308" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O308" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38508,7 +38536,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38532,17 +38560,17 @@
       </c>
       <c r="X308" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA308" s="2" t="inlineStr">
@@ -38552,17 +38580,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -38628,7 +38656,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
